--- a/SymWebNew/Files/Export/PF of-Jul-24 (15).xlsx
+++ b/SymWebNew/Files/Export/PF of-Jul-24 (15).xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="5" lowestEdited="5" rupBuild="9303"/>
   <workbookPr defaultThemeVersion="124226"/>
   <bookViews>
-    <workbookView xWindow="630" yWindow="585" windowWidth="27495" windowHeight="13740"/>
+    <workbookView xWindow="630" yWindow="570" windowWidth="27495" windowHeight="11700"/>
   </bookViews>
   <sheets>
     <sheet name="Contribution" sheetId="1" r:id="rId1"/>
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="17" uniqueCount="16">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="235" uniqueCount="103">
   <si>
     <t>EmpCode</t>
   </si>
@@ -31,10 +31,7 @@
     <t>Department</t>
   </si>
   <si>
-    <t>Section</t>
-  </si>
-  <si>
-    <t>Project</t>
+    <t>UnitName</t>
   </si>
   <si>
     <t>BasicSalary</t>
@@ -52,16 +49,280 @@
     <t>Salary Period</t>
   </si>
   <si>
-    <t>1001</t>
-  </si>
-  <si>
-    <t>Enter Name</t>
-  </si>
-  <si>
-    <t>Development</t>
+    <t>DGT000023</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Md. Rana Naser  </t>
+  </si>
+  <si>
+    <t>Senior Merchandiser</t>
+  </si>
+  <si>
+    <t>Merchandising</t>
+  </si>
+  <si>
+    <t>DFL</t>
   </si>
   <si>
     <t>Jul-24</t>
+  </si>
+  <si>
+    <t>DGT000037</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Moniruzzaman Shawon  </t>
+  </si>
+  <si>
+    <t>Merchandiser</t>
+  </si>
+  <si>
+    <t>DGT000052</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Md. Aman Ullah Bahar  </t>
+  </si>
+  <si>
+    <t>Assistant Manager</t>
+  </si>
+  <si>
+    <t>DGT000053</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Mirza Fahad Bin Alam  </t>
+  </si>
+  <si>
+    <t>Deputy Manager</t>
+  </si>
+  <si>
+    <t>DGT000071</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Md. Khairul Kabir Pias  </t>
+  </si>
+  <si>
+    <t>DGT000082</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Md. Rahim Ullah  </t>
+  </si>
+  <si>
+    <t>Manager</t>
+  </si>
+  <si>
+    <t>Commercial</t>
+  </si>
+  <si>
+    <t>DGT000086</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Mohammad Anwar Hossain  </t>
+  </si>
+  <si>
+    <t>Sr. Merchandiser</t>
+  </si>
+  <si>
+    <t>DGT000088</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Masum Ahmed  </t>
+  </si>
+  <si>
+    <t>Senior Manager</t>
+  </si>
+  <si>
+    <t>DGT000206</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Md. Saifullah-Al-Mamun  </t>
+  </si>
+  <si>
+    <t>Senior Executive</t>
+  </si>
+  <si>
+    <t>Internal Audit</t>
+  </si>
+  <si>
+    <t>DGT000288</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Md. Rayhanul Islam  </t>
+  </si>
+  <si>
+    <t>Site Engineer</t>
+  </si>
+  <si>
+    <t>Operation</t>
+  </si>
+  <si>
+    <t>DGT000334</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Md.Safiqul Islam  </t>
+  </si>
+  <si>
+    <t>Driver</t>
+  </si>
+  <si>
+    <t>Support &amp; Service</t>
+  </si>
+  <si>
+    <t>DGT000346</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Md. Asad Khan  </t>
+  </si>
+  <si>
+    <t>Executive-MIS</t>
+  </si>
+  <si>
+    <t>Accounts &amp; Finance</t>
+  </si>
+  <si>
+    <t>DGT000393</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Mahabub Alam  </t>
+  </si>
+  <si>
+    <t>EMP-000001</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Hossain A. Bhuiyan, FCS  </t>
+  </si>
+  <si>
+    <t>General Manager &amp; Company Secretary</t>
+  </si>
+  <si>
+    <t>EMP-000004</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Mohammed Abul Khayer  </t>
+  </si>
+  <si>
+    <t>EMP-000019</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Md. Moshiur Rahman  </t>
+  </si>
+  <si>
+    <t>General Manager</t>
+  </si>
+  <si>
+    <t>EMP-000042</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kazi Asaduzzaman  </t>
+  </si>
+  <si>
+    <t>EMP-000045</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Noor E- Alam Siddiquee  </t>
+  </si>
+  <si>
+    <t>EMP-000046</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Md. Mehadi Hasan  </t>
+  </si>
+  <si>
+    <t>EMP-000050</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Mizanur Rahman Khan  </t>
+  </si>
+  <si>
+    <t>EMP-000052</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Mohammed Farhad Khan  </t>
+  </si>
+  <si>
+    <t>Senior DGM</t>
+  </si>
+  <si>
+    <t>EMP-000054</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Md. Shahanur Alam  </t>
+  </si>
+  <si>
+    <t>Sr. Manager</t>
+  </si>
+  <si>
+    <t>EMP-000077</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tapash Krishna Kundu  </t>
+  </si>
+  <si>
+    <t>Senior General Manager</t>
+  </si>
+  <si>
+    <t>EMP-000188</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Md. Rubel Hawlader  </t>
+  </si>
+  <si>
+    <t>Office Assistant</t>
+  </si>
+  <si>
+    <t>EMP-000231</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Mahabubur Rahman  </t>
+  </si>
+  <si>
+    <t>Executive</t>
+  </si>
+  <si>
+    <t>EMP-000272</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Md. Billal Hossen  </t>
+  </si>
+  <si>
+    <t>Jr. Executive</t>
+  </si>
+  <si>
+    <t>EMP-000291</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Nazma Begum  </t>
+  </si>
+  <si>
+    <t>Support Staff</t>
+  </si>
+  <si>
+    <t>EMP-000335</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ganesh Chakraborty  </t>
+  </si>
+  <si>
+    <t>EMP-000336</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Md. Mizanur Rahman  </t>
+  </si>
+  <si>
+    <t>EMP-000353</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Md. Suman Howlader  </t>
+  </si>
+  <si>
+    <t>EMP-000391</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MD. Jahangir Alam  </t>
+  </si>
+  <si>
+    <t>EMP-000431</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MD. Faruk Hossain  </t>
   </si>
 </sst>
 </file>
@@ -397,10 +658,10 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:L2"/>
+  <dimension ref="A1:K33"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:12">
+    <row r="1" spans="1:11">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -434,37 +695,1125 @@
       <c r="K1" t="s">
         <v>10</v>
       </c>
-      <c r="L1" t="s">
+    </row>
+    <row r="2" spans="1:11">
+      <c r="A2" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="2" spans="1:12">
-      <c r="A2" t="s">
+      <c r="B2" t="s">
         <v>12</v>
       </c>
-      <c r="B2" t="s">
+      <c r="C2">
+        <v>0</v>
+      </c>
+      <c r="D2" t="s">
         <v>13</v>
-      </c>
-      <c r="C2">
-        <v>0</v>
       </c>
       <c r="E2" t="s">
         <v>14</v>
       </c>
+      <c r="F2" t="s">
+        <v>15</v>
+      </c>
+      <c r="G2">
+        <v>0</v>
+      </c>
       <c r="H2">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="I2">
-        <v>100</v>
-      </c>
-      <c r="J2">
-        <v>1</v>
+        <v>1</v>
+      </c>
+      <c r="J2" t="s">
+        <v>16</v>
       </c>
       <c r="K2" t="s">
-        <v>15</v>
-      </c>
-      <c r="L2" t="s">
-        <v>15</v>
+        <v>16</v>
+      </c>
+    </row>
+    <row r="3" spans="1:11">
+      <c r="A3" t="s">
+        <v>17</v>
+      </c>
+      <c r="B3" t="s">
+        <v>18</v>
+      </c>
+      <c r="C3">
+        <v>0</v>
+      </c>
+      <c r="D3" t="s">
+        <v>19</v>
+      </c>
+      <c r="E3" t="s">
+        <v>14</v>
+      </c>
+      <c r="F3" t="s">
+        <v>15</v>
+      </c>
+      <c r="G3">
+        <v>0</v>
+      </c>
+      <c r="H3">
+        <v>100</v>
+      </c>
+      <c r="I3">
+        <v>1</v>
+      </c>
+      <c r="J3" t="s">
+        <v>16</v>
+      </c>
+      <c r="K3" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="4" spans="1:11">
+      <c r="A4" t="s">
+        <v>20</v>
+      </c>
+      <c r="B4" t="s">
+        <v>21</v>
+      </c>
+      <c r="C4">
+        <v>0</v>
+      </c>
+      <c r="D4" t="s">
+        <v>22</v>
+      </c>
+      <c r="E4" t="s">
+        <v>14</v>
+      </c>
+      <c r="F4" t="s">
+        <v>15</v>
+      </c>
+      <c r="G4">
+        <v>0</v>
+      </c>
+      <c r="H4">
+        <v>100</v>
+      </c>
+      <c r="I4">
+        <v>1</v>
+      </c>
+      <c r="J4" t="s">
+        <v>16</v>
+      </c>
+      <c r="K4" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="5" spans="1:11">
+      <c r="A5" t="s">
+        <v>23</v>
+      </c>
+      <c r="B5" t="s">
+        <v>24</v>
+      </c>
+      <c r="C5">
+        <v>0</v>
+      </c>
+      <c r="D5" t="s">
+        <v>25</v>
+      </c>
+      <c r="E5" t="s">
+        <v>14</v>
+      </c>
+      <c r="F5" t="s">
+        <v>15</v>
+      </c>
+      <c r="G5">
+        <v>0</v>
+      </c>
+      <c r="H5">
+        <v>100</v>
+      </c>
+      <c r="I5">
+        <v>1</v>
+      </c>
+      <c r="J5" t="s">
+        <v>16</v>
+      </c>
+      <c r="K5" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="6" spans="1:11">
+      <c r="A6" t="s">
+        <v>26</v>
+      </c>
+      <c r="B6" t="s">
+        <v>27</v>
+      </c>
+      <c r="C6">
+        <v>0</v>
+      </c>
+      <c r="D6" t="s">
+        <v>13</v>
+      </c>
+      <c r="E6" t="s">
+        <v>14</v>
+      </c>
+      <c r="F6" t="s">
+        <v>15</v>
+      </c>
+      <c r="G6">
+        <v>0</v>
+      </c>
+      <c r="H6">
+        <v>100</v>
+      </c>
+      <c r="I6">
+        <v>1</v>
+      </c>
+      <c r="J6" t="s">
+        <v>16</v>
+      </c>
+      <c r="K6" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="7" spans="1:11">
+      <c r="A7" t="s">
+        <v>28</v>
+      </c>
+      <c r="B7" t="s">
+        <v>29</v>
+      </c>
+      <c r="C7">
+        <v>0</v>
+      </c>
+      <c r="D7" t="s">
+        <v>30</v>
+      </c>
+      <c r="E7" t="s">
+        <v>31</v>
+      </c>
+      <c r="F7" t="s">
+        <v>15</v>
+      </c>
+      <c r="G7">
+        <v>0</v>
+      </c>
+      <c r="H7">
+        <v>100</v>
+      </c>
+      <c r="I7">
+        <v>1</v>
+      </c>
+      <c r="J7" t="s">
+        <v>16</v>
+      </c>
+      <c r="K7" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="8" spans="1:11">
+      <c r="A8" t="s">
+        <v>32</v>
+      </c>
+      <c r="B8" t="s">
+        <v>33</v>
+      </c>
+      <c r="C8">
+        <v>0</v>
+      </c>
+      <c r="D8" t="s">
+        <v>34</v>
+      </c>
+      <c r="E8" t="s">
+        <v>14</v>
+      </c>
+      <c r="F8" t="s">
+        <v>15</v>
+      </c>
+      <c r="G8">
+        <v>0</v>
+      </c>
+      <c r="H8">
+        <v>100</v>
+      </c>
+      <c r="I8">
+        <v>1</v>
+      </c>
+      <c r="J8" t="s">
+        <v>16</v>
+      </c>
+      <c r="K8" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="9" spans="1:11">
+      <c r="A9" t="s">
+        <v>35</v>
+      </c>
+      <c r="B9" t="s">
+        <v>36</v>
+      </c>
+      <c r="C9">
+        <v>0</v>
+      </c>
+      <c r="D9" t="s">
+        <v>37</v>
+      </c>
+      <c r="E9" t="s">
+        <v>31</v>
+      </c>
+      <c r="F9" t="s">
+        <v>15</v>
+      </c>
+      <c r="G9">
+        <v>0</v>
+      </c>
+      <c r="H9">
+        <v>100</v>
+      </c>
+      <c r="I9">
+        <v>1</v>
+      </c>
+      <c r="J9" t="s">
+        <v>16</v>
+      </c>
+      <c r="K9" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="10" spans="1:11">
+      <c r="A10" t="s">
+        <v>38</v>
+      </c>
+      <c r="B10" t="s">
+        <v>39</v>
+      </c>
+      <c r="C10">
+        <v>0</v>
+      </c>
+      <c r="D10" t="s">
+        <v>40</v>
+      </c>
+      <c r="E10" t="s">
+        <v>41</v>
+      </c>
+      <c r="F10" t="s">
+        <v>15</v>
+      </c>
+      <c r="G10">
+        <v>0</v>
+      </c>
+      <c r="H10">
+        <v>100</v>
+      </c>
+      <c r="I10">
+        <v>1</v>
+      </c>
+      <c r="J10" t="s">
+        <v>16</v>
+      </c>
+      <c r="K10" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="11" spans="1:11">
+      <c r="A11" t="s">
+        <v>42</v>
+      </c>
+      <c r="B11" t="s">
+        <v>43</v>
+      </c>
+      <c r="C11">
+        <v>0</v>
+      </c>
+      <c r="D11" t="s">
+        <v>44</v>
+      </c>
+      <c r="E11" t="s">
+        <v>45</v>
+      </c>
+      <c r="F11" t="s">
+        <v>15</v>
+      </c>
+      <c r="G11">
+        <v>0</v>
+      </c>
+      <c r="H11">
+        <v>100</v>
+      </c>
+      <c r="I11">
+        <v>1</v>
+      </c>
+      <c r="J11" t="s">
+        <v>16</v>
+      </c>
+      <c r="K11" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="12" spans="1:11">
+      <c r="A12" t="s">
+        <v>46</v>
+      </c>
+      <c r="B12" t="s">
+        <v>47</v>
+      </c>
+      <c r="C12">
+        <v>0</v>
+      </c>
+      <c r="D12" t="s">
+        <v>48</v>
+      </c>
+      <c r="E12" t="s">
+        <v>49</v>
+      </c>
+      <c r="F12" t="s">
+        <v>15</v>
+      </c>
+      <c r="G12">
+        <v>0</v>
+      </c>
+      <c r="H12">
+        <v>100</v>
+      </c>
+      <c r="I12">
+        <v>1</v>
+      </c>
+      <c r="J12" t="s">
+        <v>16</v>
+      </c>
+      <c r="K12" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="13" spans="1:11">
+      <c r="A13" t="s">
+        <v>50</v>
+      </c>
+      <c r="B13" t="s">
+        <v>51</v>
+      </c>
+      <c r="C13">
+        <v>0</v>
+      </c>
+      <c r="D13" t="s">
+        <v>52</v>
+      </c>
+      <c r="E13" t="s">
+        <v>53</v>
+      </c>
+      <c r="F13" t="s">
+        <v>15</v>
+      </c>
+      <c r="G13">
+        <v>0</v>
+      </c>
+      <c r="H13">
+        <v>100</v>
+      </c>
+      <c r="I13">
+        <v>1</v>
+      </c>
+      <c r="J13" t="s">
+        <v>16</v>
+      </c>
+      <c r="K13" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="14" spans="1:11">
+      <c r="A14" t="s">
+        <v>54</v>
+      </c>
+      <c r="B14" t="s">
+        <v>55</v>
+      </c>
+      <c r="C14">
+        <v>0</v>
+      </c>
+      <c r="D14" t="s">
+        <v>19</v>
+      </c>
+      <c r="E14" t="s">
+        <v>14</v>
+      </c>
+      <c r="F14" t="s">
+        <v>15</v>
+      </c>
+      <c r="G14">
+        <v>0</v>
+      </c>
+      <c r="H14">
+        <v>100</v>
+      </c>
+      <c r="I14">
+        <v>1</v>
+      </c>
+      <c r="J14" t="s">
+        <v>16</v>
+      </c>
+      <c r="K14" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="15" spans="1:11">
+      <c r="A15" t="s">
+        <v>56</v>
+      </c>
+      <c r="B15" t="s">
+        <v>57</v>
+      </c>
+      <c r="C15">
+        <v>0</v>
+      </c>
+      <c r="D15" t="s">
+        <v>58</v>
+      </c>
+      <c r="E15" t="s">
+        <v>53</v>
+      </c>
+      <c r="F15" t="s">
+        <v>15</v>
+      </c>
+      <c r="G15">
+        <v>0</v>
+      </c>
+      <c r="H15">
+        <v>100</v>
+      </c>
+      <c r="I15">
+        <v>1</v>
+      </c>
+      <c r="J15" t="s">
+        <v>16</v>
+      </c>
+      <c r="K15" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="16" spans="1:11">
+      <c r="A16" t="s">
+        <v>59</v>
+      </c>
+      <c r="B16" t="s">
+        <v>60</v>
+      </c>
+      <c r="C16">
+        <v>0</v>
+      </c>
+      <c r="D16" t="s">
+        <v>30</v>
+      </c>
+      <c r="E16" t="s">
+        <v>53</v>
+      </c>
+      <c r="F16" t="s">
+        <v>15</v>
+      </c>
+      <c r="G16">
+        <v>0</v>
+      </c>
+      <c r="H16">
+        <v>100</v>
+      </c>
+      <c r="I16">
+        <v>1</v>
+      </c>
+      <c r="J16" t="s">
+        <v>16</v>
+      </c>
+      <c r="K16" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="17" spans="1:11">
+      <c r="A17" t="s">
+        <v>61</v>
+      </c>
+      <c r="B17" t="s">
+        <v>62</v>
+      </c>
+      <c r="C17">
+        <v>0</v>
+      </c>
+      <c r="D17" t="s">
+        <v>63</v>
+      </c>
+      <c r="E17" t="s">
+        <v>31</v>
+      </c>
+      <c r="F17" t="s">
+        <v>15</v>
+      </c>
+      <c r="G17">
+        <v>0</v>
+      </c>
+      <c r="H17">
+        <v>100</v>
+      </c>
+      <c r="I17">
+        <v>1</v>
+      </c>
+      <c r="J17" t="s">
+        <v>16</v>
+      </c>
+      <c r="K17" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="18" spans="1:11">
+      <c r="A18" t="s">
+        <v>64</v>
+      </c>
+      <c r="B18" t="s">
+        <v>65</v>
+      </c>
+      <c r="C18">
+        <v>0</v>
+      </c>
+      <c r="D18" t="s">
+        <v>37</v>
+      </c>
+      <c r="E18" t="s">
+        <v>14</v>
+      </c>
+      <c r="F18" t="s">
+        <v>15</v>
+      </c>
+      <c r="G18">
+        <v>0</v>
+      </c>
+      <c r="H18">
+        <v>100</v>
+      </c>
+      <c r="I18">
+        <v>1</v>
+      </c>
+      <c r="J18" t="s">
+        <v>16</v>
+      </c>
+      <c r="K18" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="19" spans="1:11">
+      <c r="A19" t="s">
+        <v>66</v>
+      </c>
+      <c r="B19" t="s">
+        <v>67</v>
+      </c>
+      <c r="C19">
+        <v>0</v>
+      </c>
+      <c r="D19" t="s">
+        <v>63</v>
+      </c>
+      <c r="E19" t="s">
+        <v>14</v>
+      </c>
+      <c r="F19" t="s">
+        <v>15</v>
+      </c>
+      <c r="G19">
+        <v>0</v>
+      </c>
+      <c r="H19">
+        <v>100</v>
+      </c>
+      <c r="I19">
+        <v>1</v>
+      </c>
+      <c r="J19" t="s">
+        <v>16</v>
+      </c>
+      <c r="K19" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="20" spans="1:11">
+      <c r="A20" t="s">
+        <v>68</v>
+      </c>
+      <c r="B20" t="s">
+        <v>69</v>
+      </c>
+      <c r="C20">
+        <v>0</v>
+      </c>
+      <c r="D20" t="s">
+        <v>22</v>
+      </c>
+      <c r="E20" t="s">
+        <v>14</v>
+      </c>
+      <c r="F20" t="s">
+        <v>15</v>
+      </c>
+      <c r="G20">
+        <v>0</v>
+      </c>
+      <c r="H20">
+        <v>100</v>
+      </c>
+      <c r="I20">
+        <v>1</v>
+      </c>
+      <c r="J20" t="s">
+        <v>16</v>
+      </c>
+      <c r="K20" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="21" spans="1:11">
+      <c r="A21" t="s">
+        <v>70</v>
+      </c>
+      <c r="B21" t="s">
+        <v>71</v>
+      </c>
+      <c r="C21">
+        <v>0</v>
+      </c>
+      <c r="D21" t="s">
+        <v>25</v>
+      </c>
+      <c r="E21" t="s">
+        <v>14</v>
+      </c>
+      <c r="F21" t="s">
+        <v>15</v>
+      </c>
+      <c r="G21">
+        <v>0</v>
+      </c>
+      <c r="H21">
+        <v>100</v>
+      </c>
+      <c r="I21">
+        <v>1</v>
+      </c>
+      <c r="J21" t="s">
+        <v>16</v>
+      </c>
+      <c r="K21" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="22" spans="1:11">
+      <c r="A22" t="s">
+        <v>72</v>
+      </c>
+      <c r="B22" t="s">
+        <v>73</v>
+      </c>
+      <c r="C22">
+        <v>0</v>
+      </c>
+      <c r="D22" t="s">
+        <v>74</v>
+      </c>
+      <c r="E22" t="s">
+        <v>14</v>
+      </c>
+      <c r="F22" t="s">
+        <v>15</v>
+      </c>
+      <c r="G22">
+        <v>0</v>
+      </c>
+      <c r="H22">
+        <v>100</v>
+      </c>
+      <c r="I22">
+        <v>1</v>
+      </c>
+      <c r="J22" t="s">
+        <v>16</v>
+      </c>
+      <c r="K22" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="23" spans="1:11">
+      <c r="A23" t="s">
+        <v>75</v>
+      </c>
+      <c r="B23" t="s">
+        <v>76</v>
+      </c>
+      <c r="C23">
+        <v>0</v>
+      </c>
+      <c r="D23" t="s">
+        <v>77</v>
+      </c>
+      <c r="E23" t="s">
+        <v>14</v>
+      </c>
+      <c r="F23" t="s">
+        <v>15</v>
+      </c>
+      <c r="G23">
+        <v>0</v>
+      </c>
+      <c r="H23">
+        <v>100</v>
+      </c>
+      <c r="I23">
+        <v>1</v>
+      </c>
+      <c r="J23" t="s">
+        <v>16</v>
+      </c>
+      <c r="K23" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="24" spans="1:11">
+      <c r="A24" t="s">
+        <v>78</v>
+      </c>
+      <c r="B24" t="s">
+        <v>79</v>
+      </c>
+      <c r="C24">
+        <v>0</v>
+      </c>
+      <c r="D24" t="s">
+        <v>80</v>
+      </c>
+      <c r="E24" t="s">
+        <v>45</v>
+      </c>
+      <c r="F24" t="s">
+        <v>15</v>
+      </c>
+      <c r="G24">
+        <v>0</v>
+      </c>
+      <c r="H24">
+        <v>100</v>
+      </c>
+      <c r="I24">
+        <v>1</v>
+      </c>
+      <c r="J24" t="s">
+        <v>16</v>
+      </c>
+      <c r="K24" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="25" spans="1:11">
+      <c r="A25" t="s">
+        <v>81</v>
+      </c>
+      <c r="B25" t="s">
+        <v>82</v>
+      </c>
+      <c r="C25">
+        <v>0</v>
+      </c>
+      <c r="D25" t="s">
+        <v>83</v>
+      </c>
+      <c r="E25" t="s">
+        <v>49</v>
+      </c>
+      <c r="F25" t="s">
+        <v>15</v>
+      </c>
+      <c r="G25">
+        <v>0</v>
+      </c>
+      <c r="H25">
+        <v>100</v>
+      </c>
+      <c r="I25">
+        <v>1</v>
+      </c>
+      <c r="J25" t="s">
+        <v>16</v>
+      </c>
+      <c r="K25" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="26" spans="1:11">
+      <c r="A26" t="s">
+        <v>84</v>
+      </c>
+      <c r="B26" t="s">
+        <v>85</v>
+      </c>
+      <c r="C26">
+        <v>0</v>
+      </c>
+      <c r="D26" t="s">
+        <v>86</v>
+      </c>
+      <c r="E26" t="s">
+        <v>45</v>
+      </c>
+      <c r="F26" t="s">
+        <v>15</v>
+      </c>
+      <c r="G26">
+        <v>0</v>
+      </c>
+      <c r="H26">
+        <v>100</v>
+      </c>
+      <c r="I26">
+        <v>1</v>
+      </c>
+      <c r="J26" t="s">
+        <v>16</v>
+      </c>
+      <c r="K26" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="27" spans="1:11">
+      <c r="A27" t="s">
+        <v>87</v>
+      </c>
+      <c r="B27" t="s">
+        <v>88</v>
+      </c>
+      <c r="C27">
+        <v>0</v>
+      </c>
+      <c r="D27" t="s">
+        <v>89</v>
+      </c>
+      <c r="E27" t="s">
+        <v>31</v>
+      </c>
+      <c r="F27" t="s">
+        <v>15</v>
+      </c>
+      <c r="G27">
+        <v>0</v>
+      </c>
+      <c r="H27">
+        <v>100</v>
+      </c>
+      <c r="I27">
+        <v>1</v>
+      </c>
+      <c r="J27" t="s">
+        <v>16</v>
+      </c>
+      <c r="K27" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="28" spans="1:11">
+      <c r="A28" t="s">
+        <v>90</v>
+      </c>
+      <c r="B28" t="s">
+        <v>91</v>
+      </c>
+      <c r="C28">
+        <v>0</v>
+      </c>
+      <c r="D28" t="s">
+        <v>92</v>
+      </c>
+      <c r="E28" t="s">
+        <v>49</v>
+      </c>
+      <c r="F28" t="s">
+        <v>15</v>
+      </c>
+      <c r="G28">
+        <v>0</v>
+      </c>
+      <c r="H28">
+        <v>100</v>
+      </c>
+      <c r="I28">
+        <v>1</v>
+      </c>
+      <c r="J28" t="s">
+        <v>16</v>
+      </c>
+      <c r="K28" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="29" spans="1:11">
+      <c r="A29" t="s">
+        <v>93</v>
+      </c>
+      <c r="B29" t="s">
+        <v>94</v>
+      </c>
+      <c r="C29">
+        <v>0</v>
+      </c>
+      <c r="D29" t="s">
+        <v>83</v>
+      </c>
+      <c r="E29" t="s">
+        <v>49</v>
+      </c>
+      <c r="F29" t="s">
+        <v>15</v>
+      </c>
+      <c r="G29">
+        <v>0</v>
+      </c>
+      <c r="H29">
+        <v>100</v>
+      </c>
+      <c r="I29">
+        <v>1</v>
+      </c>
+      <c r="J29" t="s">
+        <v>16</v>
+      </c>
+      <c r="K29" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="30" spans="1:11">
+      <c r="A30" t="s">
+        <v>95</v>
+      </c>
+      <c r="B30" t="s">
+        <v>96</v>
+      </c>
+      <c r="C30">
+        <v>0</v>
+      </c>
+      <c r="D30" t="s">
+        <v>83</v>
+      </c>
+      <c r="E30" t="s">
+        <v>49</v>
+      </c>
+      <c r="F30" t="s">
+        <v>15</v>
+      </c>
+      <c r="G30">
+        <v>0</v>
+      </c>
+      <c r="H30">
+        <v>100</v>
+      </c>
+      <c r="I30">
+        <v>1</v>
+      </c>
+      <c r="J30" t="s">
+        <v>16</v>
+      </c>
+      <c r="K30" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="31" spans="1:11">
+      <c r="A31" t="s">
+        <v>97</v>
+      </c>
+      <c r="B31" t="s">
+        <v>98</v>
+      </c>
+      <c r="C31">
+        <v>0</v>
+      </c>
+      <c r="D31" t="s">
+        <v>40</v>
+      </c>
+      <c r="E31" t="s">
+        <v>31</v>
+      </c>
+      <c r="F31" t="s">
+        <v>15</v>
+      </c>
+      <c r="G31">
+        <v>0</v>
+      </c>
+      <c r="H31">
+        <v>100</v>
+      </c>
+      <c r="I31">
+        <v>1</v>
+      </c>
+      <c r="J31" t="s">
+        <v>16</v>
+      </c>
+      <c r="K31" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="32" spans="1:11">
+      <c r="A32" t="s">
+        <v>99</v>
+      </c>
+      <c r="B32" t="s">
+        <v>100</v>
+      </c>
+      <c r="C32">
+        <v>0</v>
+      </c>
+      <c r="D32" t="s">
+        <v>83</v>
+      </c>
+      <c r="E32" t="s">
+        <v>49</v>
+      </c>
+      <c r="F32" t="s">
+        <v>15</v>
+      </c>
+      <c r="G32">
+        <v>0</v>
+      </c>
+      <c r="H32">
+        <v>100</v>
+      </c>
+      <c r="I32">
+        <v>1</v>
+      </c>
+      <c r="J32" t="s">
+        <v>16</v>
+      </c>
+      <c r="K32" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="33" spans="1:11">
+      <c r="A33" t="s">
+        <v>101</v>
+      </c>
+      <c r="B33" t="s">
+        <v>102</v>
+      </c>
+      <c r="C33">
+        <v>0</v>
+      </c>
+      <c r="D33" t="s">
+        <v>83</v>
+      </c>
+      <c r="E33" t="s">
+        <v>49</v>
+      </c>
+      <c r="F33" t="s">
+        <v>15</v>
+      </c>
+      <c r="G33">
+        <v>0</v>
+      </c>
+      <c r="H33">
+        <v>100</v>
+      </c>
+      <c r="I33">
+        <v>1</v>
+      </c>
+      <c r="J33" t="s">
+        <v>16</v>
+      </c>
+      <c r="K33" t="s">
+        <v>16</v>
       </c>
     </row>
   </sheetData>
